--- a/Output/Tables/table1_baseline.xlsx
+++ b/Output/Tables/table1_baseline.xlsx
@@ -351,7 +351,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>[ALL]   N=2058</t>
+          <t>[ALL]   N=1963</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -368,12 +368,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1573 (76.4%)  </t>
+          <t xml:space="preserve">  1490 (75.9%)  </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -385,12 +385,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1475 (71.7%)  </t>
+          <t xml:space="preserve">  1397 (71.2%)  </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -402,12 +402,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  88.7 (10.1)   </t>
+          <t xml:space="preserve">  88.7 (10.0)   </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -419,12 +419,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.19 (3.12)   </t>
+          <t xml:space="preserve">  3.17 (3.12)   </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -436,12 +436,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1933 (93.9%)  </t>
+          <t xml:space="preserve">  1840 (93.7%)  </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -453,12 +453,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11.4 (4.55)   </t>
+          <t xml:space="preserve">  11.4 (4.56)   </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>1951</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>1951</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">784 </t>
+          <t xml:space="preserve">748 </t>
         </is>
       </c>
     </row>
@@ -504,12 +504,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1585 (77.0%)  </t>
+          <t xml:space="preserve">  1511 (77.0%)  </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  162 (7.87%)   </t>
+          <t xml:space="preserve">  159 (8.10%)   </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  215 (10.4%)   </t>
+          <t xml:space="preserve">  204 (10.4%)   </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  261 (12.7%)   </t>
+          <t xml:space="preserve">  248 (12.6%)   </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  476 (23.1%)   </t>
+          <t xml:space="preserve">  453 (23.1%)   </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1031 (50.1%)  </t>
+          <t xml:space="preserve">  988 (50.3%)   </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   31 (1.51%)   </t>
+          <t xml:space="preserve">   29 (1.48%)   </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   44 (2.14%)   </t>
+          <t xml:space="preserve">   41 (2.09%)   </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1095 (53.2%)  </t>
+          <t xml:space="preserve">  1052 (53.6%)  </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  301 (14.6%)   </t>
+          <t xml:space="preserve">  289 (14.7%)   </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  275 (13.4%)   </t>
+          <t xml:space="preserve">  257 (13.1%)   </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  335 (16.3%)   </t>
+          <t xml:space="preserve">  316 (16.1%)   </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   52 (2.53%)   </t>
+          <t xml:space="preserve">   49 (2.50%)   </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  252 (12.2%)   </t>
+          <t xml:space="preserve">  242 (12.3%)   </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   8 (0.39%)    </t>
+          <t xml:space="preserve">   8 (0.41%)    </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1044 (50.7%)  </t>
+          <t xml:space="preserve">  992 (50.5%)   </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  754 (36.6%)   </t>
+          <t xml:space="preserve">  721 (36.7%)   </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1008 (49.0%)  </t>
+          <t xml:space="preserve">  961 (49.0%)   </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  241 (11.7%)   </t>
+          <t xml:space="preserve">  219 (11.2%)   </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  809 (39.3%)   </t>
+          <t xml:space="preserve">  783 (39.9%)   </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.52 (0.95)   </t>
+          <t xml:space="preserve">  0.51 (0.95)   </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1923</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  397 (19.3%)   </t>
+          <t xml:space="preserve">  374 (19.1%)   </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  535 (26.0%)   </t>
+          <t xml:space="preserve">  505 (25.7%)   </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">77.1 [52.1;100] </t>
+          <t xml:space="preserve">77.8 [52.9;100] </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>46.2 [22.2;69.9]</t>
+          <t>45.9 [21.4;69.5]</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">88.2 [72.7;100] </t>
+          <t xml:space="preserve">88.5 [73.3;100] </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">  410 (19.9%)   </t>
+          <t xml:space="preserve">  395 (20.1%)   </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  299 (14.5%)   </t>
+          <t xml:space="preserve">  260 (13.2%)   </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  202 (9.82%)   </t>
+          <t xml:space="preserve">  194 (9.88%)   </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  165 (8.02%)   </t>
+          <t xml:space="preserve">  159 (8.10%)   </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  298 (14.5%)   </t>
+          <t xml:space="preserve">  292 (14.9%)   </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  351 (17.1%)   </t>
+          <t xml:space="preserve">  344 (17.5%)   </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">  333 (16.2%)   </t>
+          <t xml:space="preserve">  319 (16.3%)   </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  743 (36.1%)   </t>
+          <t xml:space="preserve">  714 (36.4%)   </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">  299 (14.5%)   </t>
+          <t xml:space="preserve">  260 (13.2%)   </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1016 (49.4%)  </t>
+          <t xml:space="preserve">  989 (50.4%)   </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">  743 (36.1%)   </t>
+          <t xml:space="preserve">  714 (36.4%)   </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">  299 (14.5%)   </t>
+          <t xml:space="preserve">  260 (13.2%)   </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">  367 (17.8%)   </t>
+          <t xml:space="preserve">  353 (18.0%)   </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">  649 (31.5%)   </t>
+          <t xml:space="preserve">  636 (32.4%)   </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">   258 (156)    </t>
+          <t xml:space="preserve">   259 (156)    </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">   294 (146)    </t>
+          <t xml:space="preserve">   295 (146)    </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1963</t>
         </is>
       </c>
     </row>
